--- a/data_extactor/batch_10_fa/trimmed/batch_0063_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0063_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | محاسبات عددی | استدلال ریاضی</t>
+          <t>درک شفاهی | بینایی نزدیک | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>صندوق‌داران | متصدیان پذیرش و باجه اجاره خدمات | سرپرستان رده‌اول کارکنان خدمات تفریحی و بازی | کارکنان بخش خزانه‌داری مراکز بازی | متصدیان پذیرش هتل، متل و مجتمع‌های اقامتی | متصدیان افتتاح حساب جدید | تحویل‌داران بانکی</t>
+          <t>صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | متصدیان باجه و خزانه‌داری مراکز بازی و سرگرمی | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان افتتاح حساب | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | فروش و بازاریابی | مدیریت و امور اداری | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | فروش و بازاریابی | مدیریت و اداره | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>صندوق‌داران | کارشناسان خدمات پس از فروش و امور مشتریان | متصدیان پذیرش هتل، متل و مجتمع‌های اقامتی | کارشناسان ثبت و پیگیری سفارش‌ها | فروشندگان قطعات و لوازم یدکی | متصدیان پذیرش و پاسخگویی اطلاعات | فروشندگان خرده‌فروشی</t>
+          <t>صندوق‌داران | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان ثبت و پیگیری سفارش‌ها | فروشندگان قطعات و لوازم یدکی | متصدیان پذیرش و اطلاعات | فروشندگان خرده‌فروشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | مدیریت و امور اداری | امور اداری و دفتری | رایانه و الکترونیک | امور فنی و مکانیک</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره | اداری | رایانه و الکترونیک | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | تشخیص گفتار | درک کتبی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | درک کتبی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و تعمیرکاران خودرو | متصدیان باجه و کرایه کالا و خدمات | تعمیرکاران لوازم خانگی | کارشناسان ثبت و پیگیری سفارش‌ها | فروشندگان خرده‌فروشی | کارشناسان انبارداری، دریافت، ارسال و کنترل موجودی | متصدیان چیدمان و آماده‌سازی سفارش‌ها</t>
+          <t>مکانیک و تکنسین خدمات خودرو | متصدیان باجه و کرایه کالا و خدمات | تعمیرکاران لوازم خانگی | متصدیان ثبت و پیگیری سفارش‌ها | فروشندگان خرده‌فروشی | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | نگارش | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مدیریت و امور اداری | ریاضیات | امور اداری و دفتری</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | مدیریت و اداره | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | دید نزدیک | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات پس از فروش و امور مشتریان | سرپرستان رده‌اول فروشگاه‌های خرده‌فروشی | طراحان چیدمان و دکوراسیون ویترین فروشگاه‌ها | فروشندگان قطعات و لوازم یدکی | متصدیان چیدمان و آماده‌سازی سفارش‌ها</t>
+          <t>صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | سرپرستان رده‌اول فروشندگان خرده‌فروشی | طراحان دکوراسیون و ویترین مغازه | فروشندگان قطعات و لوازم یدکی | متصدیان چیدمان و آماده‌سازی سفارش</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | خدمات مشتریان و خدمات فردی | ارتباطات و رسانه | ریاضیات | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | ارتباطات و رسانه | ریاضیات | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | تشخیص گفتار | درک کتبی | بیان کتبی | ابتکار و اصالت</t>
+          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | تشخیص گفتار | درک کتبی | بیان کتبی | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران تبلیغات و روابط عمومی | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | مدیران بازاریابی | گردانندگان و مدیران فروشگاه‌های اینترنتی | کارشناسان روابط عمومی | مدیران فروش | استراتژیست‌های بازاریابی موتورهای جستجو</t>
+          <t>مدیران تبلیغات و روابط ترویجی | کارشناسان تحلیل تحقیقات بازار و بازاریابی | مدیران بازاریابی | کارشناسان تجارت الکترونیک و فروشگاه‌های اینترنتی | کارشناسان روابط عمومی | مدیران فروش | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | ریاضیات | حقوق و مقررات دولتی | مدیریت و امور اداری | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | ریاضیات | قانون و دولت | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان ارزیابی، بررسی و خسارت بیمه | مشاوران اعتباری و مالی | کارشناسان خدمات پس از فروش و امور مشتریان | کارشناسان صدور و رسیدگی به خسارت‌های بیمه | کارشناسان صدور و ارزیابی ریسک بیمه‌نامه (آندروایتر) | مشاوران مالی شخصی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی</t>
+          <t>کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | مشاوران اعتباری و مدیریت بدهی | کارشناسان خدمات و پشتیبانی مشتریان | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | مشاوران مالی فردی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب | سخن گفتن | نگارش | ریاضیات</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب | سخن گفتن | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | ریاضیات | فروش و بازاریابی | رایانه و الکترونیک | حقوق و مقررات دولتی</t>
+          <t>خدمات مشتری و شخصی | اقتصاد و حسابداری | ریاضیات | فروش و بازاریابی | رایانه و الکترونیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان امور اداری کارگزاری‌ها | تحلیل‌گران اعتباری | مدیران مالی | تحلیل‌گران مالی و سرمایه‌گذاری | مدیران صندوق‌های سرمایه‌گذاری | مشاوران مالی شخصی | تحویل‌داران بانکی</t>
+          <t>کارشناسان امور اداری و معاملات کارگزاری | تحلیل‌گران اعتبارات و تسهیلات | مدیران امور مالی | تحلیل‌گران مالی و سرمایه‌گذاری | مدیران صندوق‌های سرمایه‌گذاری | مشاوران مالی فردی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فروش و بازاریابی | جغرافیا | رایانه و الکترونیک | امور حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فروش و بازاریابی | جغرافیا | رایانه و الکترونیک | حمل و نقل</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>تشخیص گفتار | درک شفاهی | وضوح گفتار | درک کتبی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>تشخیص گفتار | درک شفاهی | وضوح گفتار | درک کتبی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>راهنمایان و مسئولان خدمات تشریفات و اقامت (Concierge) | متصدیان باجه و کرایه کالا و خدمات | متصدیان پذیرش هتل، متل و مجتمع‌های اقامتی | برنامه‌ریزان همایش‌ها، نشست‌ها و رویدادها | کارشناسان رزرواسیون و صدور بلیط سفر | راهنمایان و سرپرستان تورهای گردشگری (تور لیدر) | راهنمایان محلی سفر</t>
+          <t>متصدیان تشریفات و خدمات میهمانان | متصدیان باجه و کرایه کالا و خدمات | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | راهنمایان تور و گردشگری | راهنمایان گردشگری و تور</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | اقتصاد و حسابداری | ارتباطات و رسانه | رایانه و الکترونیک</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | مدیریت و اداره | اقتصاد و حسابداری | ارتباطات و رسانه | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کارشناسان فروش فضاهای تبلیغاتی | کارشناسان خدمات پس از فروش و امور مشتریان | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | کارشناسان فروش بیمه | مهندسان فروش | مدیران فروش | کارشناسان فروش عمده و صنعتی (کالاهای فنی و علمی)</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | کارشناسان خدمات و پشتیبانی مشتریان | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | نمایندگان و کارشناسان فروش بیمه | مهندسان فروش | مدیران فروش | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | یادگیری فعال | نگارش | تفکر انتقادی | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | زبان انگلیسی | مدیریت و امور اداری | ریاضیات | تولید و فرآوری | رایانه و الکترونیک</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | زبان انگلیسی | مدیریت و اداره | ریاضیات | تولید و فرآوری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کارشناسان خدمات پس از فروش و امور مشتریان | مهندسان صنایع | کارشناسان لجستیک و زنجیره تامین | فروشندگان قطعات و لوازم یدکی | مدیران خرید و تدارکات | مهندسان فروش | مدیران فروش</t>
+          <t>کارشناسان خدمات و پشتیبانی مشتریان | مهندسان صنایع | کارشناسان لجستیک و مدیریت زنجیره تأمین | فروشندگان قطعات و لوازم یدکی | مدیران خرید و تدارکات | مهندسان فروش | مدیران فروش</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
